--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126838692</v>
       </c>
       <c r="B2" t="n">
-        <v>91259</v>
+        <v>91333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126838689</v>
       </c>
       <c r="B3" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126838692</v>
       </c>
       <c r="B2" t="n">
-        <v>91333</v>
+        <v>91339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126838689</v>
       </c>
       <c r="B3" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126838692</v>
       </c>
       <c r="B2" t="n">
-        <v>91339</v>
+        <v>91340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126838692</v>
       </c>
       <c r="B2" t="n">
-        <v>91340</v>
+        <v>91344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126838689</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,6 +867,699 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127836044</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100638</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>534435</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6762291</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127833509</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100638</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>534385</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6762291</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127835009</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Trollberget, Trollberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>534141</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6762421</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127836051</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100545</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>534429</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6762300</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127834926</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80123</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Trollberget, Trollberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>534166</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6762291</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Troligtvis död, på död rönn.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127833519</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100545</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>534385</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6762289</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127835398</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91338</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>534296</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6762499</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127836044</v>
       </c>
       <c r="B4" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127833509</v>
       </c>
       <c r="B5" t="n">
-        <v>100638</v>
+        <v>100641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127835009</v>
       </c>
       <c r="B6" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127836051</v>
       </c>
       <c r="B7" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127834926</v>
       </c>
       <c r="B8" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127833519</v>
       </c>
       <c r="B9" t="n">
-        <v>100545</v>
+        <v>100548</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>127835398</v>
       </c>
       <c r="B10" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127836044</v>
       </c>
       <c r="B4" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127833509</v>
       </c>
       <c r="B5" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127835009</v>
       </c>
       <c r="B6" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127836051</v>
       </c>
       <c r="B7" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127834926</v>
       </c>
       <c r="B8" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127833519</v>
       </c>
       <c r="B9" t="n">
-        <v>100548</v>
+        <v>100556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>127835398</v>
       </c>
       <c r="B10" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127836044</v>
       </c>
       <c r="B4" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127833509</v>
       </c>
       <c r="B5" t="n">
-        <v>100649</v>
+        <v>100650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127836051</v>
       </c>
       <c r="B7" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127833519</v>
       </c>
       <c r="B9" t="n">
-        <v>100556</v>
+        <v>100557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>127835398</v>
       </c>
       <c r="B10" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127836044</v>
       </c>
       <c r="B4" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127833509</v>
       </c>
       <c r="B5" t="n">
-        <v>100650</v>
+        <v>100651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127836051</v>
       </c>
       <c r="B7" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127833519</v>
       </c>
       <c r="B9" t="n">
-        <v>100557</v>
+        <v>100558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>127835398</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127836044</v>
       </c>
       <c r="B4" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127833509</v>
       </c>
       <c r="B5" t="n">
-        <v>100651</v>
+        <v>100652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127836051</v>
       </c>
       <c r="B7" t="n">
-        <v>100558</v>
+        <v>100559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127833519</v>
       </c>
       <c r="B9" t="n">
-        <v>100558</v>
+        <v>100559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>127835398</v>
       </c>
       <c r="B10" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127835009</v>
+        <v>127836051</v>
       </c>
       <c r="B6" t="n">
-        <v>56864</v>
+        <v>100559</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,43 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trollberget, Trollberget, Dlr</t>
+          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534141</v>
+        <v>534429</v>
       </c>
       <c r="R6" t="n">
-        <v>6762421</v>
+        <v>6762300</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127836051</v>
+        <v>127835009</v>
       </c>
       <c r="B7" t="n">
-        <v>100559</v>
+        <v>56864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,34 +1171,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
+          <t>Trollberget, Trollberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534429</v>
+        <v>534141</v>
       </c>
       <c r="R7" t="n">
-        <v>6762300</v>
+        <v>6762421</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127836051</v>
+        <v>127835009</v>
       </c>
       <c r="B6" t="n">
-        <v>100559</v>
+        <v>56864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1074,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
+          <t>Trollberget, Trollberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534429</v>
+        <v>534141</v>
       </c>
       <c r="R6" t="n">
-        <v>6762300</v>
+        <v>6762421</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127835009</v>
+        <v>127836051</v>
       </c>
       <c r="B7" t="n">
-        <v>56864</v>
+        <v>100559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,43 +1180,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trollberget, Trollberget, Dlr</t>
+          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534141</v>
+        <v>534429</v>
       </c>
       <c r="R7" t="n">
-        <v>6762421</v>
+        <v>6762300</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127836044</v>
       </c>
       <c r="B4" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127833509</v>
       </c>
       <c r="B5" t="n">
-        <v>100652</v>
+        <v>100660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127836051</v>
       </c>
       <c r="B7" t="n">
-        <v>100559</v>
+        <v>100567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127834926</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127833519</v>
       </c>
       <c r="B9" t="n">
-        <v>100559</v>
+        <v>100567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>127835398</v>
       </c>
       <c r="B10" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127836044</v>
       </c>
       <c r="B4" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127833509</v>
       </c>
       <c r="B5" t="n">
-        <v>100660</v>
+        <v>100753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127835009</v>
+        <v>127836051</v>
       </c>
       <c r="B6" t="n">
-        <v>56864</v>
+        <v>100660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,43 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trollberget, Trollberget, Dlr</t>
+          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534141</v>
+        <v>534429</v>
       </c>
       <c r="R6" t="n">
-        <v>6762421</v>
+        <v>6762300</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127836051</v>
+        <v>127835009</v>
       </c>
       <c r="B7" t="n">
-        <v>100567</v>
+        <v>56876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,34 +1171,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
+          <t>Trollberget, Trollberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534429</v>
+        <v>534141</v>
       </c>
       <c r="R7" t="n">
-        <v>6762300</v>
+        <v>6762421</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1269,7 +1269,7 @@
         <v>127834926</v>
       </c>
       <c r="B8" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127833519</v>
       </c>
       <c r="B9" t="n">
-        <v>100567</v>
+        <v>100660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>127835398</v>
       </c>
       <c r="B10" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127836051</v>
+        <v>127835009</v>
       </c>
       <c r="B6" t="n">
-        <v>100660</v>
+        <v>56876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1074,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
+          <t>Trollberget, Trollberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534429</v>
+        <v>534141</v>
       </c>
       <c r="R6" t="n">
-        <v>6762300</v>
+        <v>6762421</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127835009</v>
+        <v>127836051</v>
       </c>
       <c r="B7" t="n">
-        <v>56876</v>
+        <v>100660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,43 +1180,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trollberget, Trollberget, Dlr</t>
+          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534141</v>
+        <v>534429</v>
       </c>
       <c r="R7" t="n">
-        <v>6762421</v>
+        <v>6762300</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127835009</v>
+        <v>127836051</v>
       </c>
       <c r="B6" t="n">
-        <v>56876</v>
+        <v>100660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,43 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trollberget, Trollberget, Dlr</t>
+          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534141</v>
+        <v>534429</v>
       </c>
       <c r="R6" t="n">
-        <v>6762421</v>
+        <v>6762300</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127836051</v>
+        <v>127835009</v>
       </c>
       <c r="B7" t="n">
-        <v>100660</v>
+        <v>56876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,34 +1171,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gräsbergsmyren, Gräsbergsmyren, Dlr</t>
+          <t>Trollberget, Trollberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534429</v>
+        <v>534141</v>
       </c>
       <c r="R7" t="n">
-        <v>6762300</v>
+        <v>6762421</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126838692</v>
       </c>
       <c r="B2" t="n">
-        <v>91344</v>
+        <v>91333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126838689</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>80143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36849-2025 artfynd.xlsx
+++ b/artfynd/A 36849-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126838692</v>
       </c>
       <c r="B2" t="n">
-        <v>91333</v>
+        <v>91344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126838689</v>
       </c>
       <c r="B3" t="n">
-        <v>80143</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
